--- a/FAO-dsd/DSD_FI_PRODUCTION.xlsx
+++ b/FAO-dsd/DSD_FI_PRODUCTION.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27425"/>
   <workbookPr autoCompressPictures="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unfao-my.sharepoint.com/personal/sara_montanaro_fao_org/Documents/DISSEMINATED_CSV/2024/GlobalProduction_2024.1.0/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="11_2D28B2D2886775EAEC912923E0A64D6BE8329EE8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{543E183E-4BC4-40FB-A87B-97FD5FE3A8F4}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="11_2D28B2D2886775EAEC912923E0A64D6BE8329EE8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{58A2F998-F256-4CF2-AFFC-C766C22EE181}"/>
   <bookViews>
-    <workbookView xWindow="3330" yWindow="5955" windowWidth="22050" windowHeight="7905" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2130" yWindow="7725" windowWidth="25950" windowHeight="9345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="7" r:id="rId1"/>
@@ -123,9 +123,6 @@
     <t>Unit</t>
   </si>
   <si>
-    <t>CL_FI_UNIT</t>
-  </si>
-  <si>
     <t>SYMBOL</t>
   </si>
   <si>
@@ -166,6 +163,9 @@
   </si>
   <si>
     <t>FAO SDMX statistical symbol</t>
+  </si>
+  <si>
+    <t>FSJ_UNIT</t>
   </si>
 </sst>
 </file>
@@ -296,6 +296,10 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -602,7 +606,7 @@
         <v>9</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>0</v>
@@ -622,13 +626,13 @@
         <v>11</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>0</v>
       </c>
       <c r="D4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E4" t="s">
         <v>18</v>
@@ -642,13 +646,13 @@
         <v>12</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>0</v>
       </c>
       <c r="D5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E5" t="s">
         <v>18</v>
@@ -662,7 +666,7 @@
         <v>13</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>2</v>
@@ -671,7 +675,7 @@
         <v>21</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>14</v>
@@ -682,7 +686,7 @@
         <v>15</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>6</v>
@@ -697,13 +701,13 @@
         <v>16</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>18</v>
@@ -717,7 +721,7 @@
         <v>17</v>
       </c>
       <c r="B9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C9" t="s">
         <v>27</v>
@@ -731,19 +735,19 @@
         <v>29</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D10" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F10" s="1" t="s">
         <v>44</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
